--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-agile-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/ba-agile-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Scrum Master là người hỗ trợ (Servant Leader), giúp Scrum Team làm việc hiệu quả bằng cách loại bỏ các rào cản và đảm bảo tuân thủ quy trình Scrum.</v>
       </c>
       <c r="F2" t="str">
-        <v>Đóng vai trò là người hỗ trợ, loại bỏ trở ngại và bảo vệ quy trình làm việc của team — servant leader</v>
+        <v>Đứng ra phân chia công việc hàng ngày và chấm công cho các thành viên — quản lý hành chính</v>
       </c>
       <c r="G2" t="str">
-        <v>Đứng ra phân chia công việc hàng ngày và chấm công cho các thành viên — quản lý hành chính</v>
+        <v>Trực tiếp thương lượng tiến độ và ký hợp đồng kinh doanh với khách hàng — account manager</v>
       </c>
       <c r="H2" t="str">
         <v>Chịu trách nhiệm thiết kế kiến trúc kỹ thuật và viết code chính của dự án — tech lead</v>
       </c>
       <c r="I2" t="str">
-        <v>Trực tiếp thương lượng tiến độ và ký hợp đồng kinh doanh với khách hàng — account manager</v>
+        <v>Đóng vai trò là người hỗ trợ, loại bỏ trở ngại và bảo vệ quy trình làm việc của team — servant leader</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
         <v>Product Backlog là danh sách duy nhất các yêu cầu, tính năng được sắp xếp theo thứ tự ưu tiên nhằm phát triển sản phẩm.</v>
       </c>
       <c r="F3" t="str">
-        <v>Danh sách ưu tiên các tính năng, yêu cầu và công việc cần thực hiện cho sản phẩm — danh sách công việc tích lũy</v>
+        <v>Bản kế hoạch kiểm thử chi tiết bao gồm tất cả các kịch bản test lỗi — kế hoạch kiểm thử</v>
       </c>
       <c r="G3" t="str">
         <v>Tài liệu báo cáo tài chính và chi phí nhân sự hàng tháng của dự án — báo cáo tài chính</v>
@@ -501,10 +501,10 @@
         <v>Sơ đồ thiết kế cơ sở dữ liệu chi tiết của toàn bộ hệ thống — sơ đồ kỹ thuật</v>
       </c>
       <c r="I3" t="str">
-        <v>Bản kế hoạch kiểm thử chi tiết bao gồm tất cả các kịch bản test lỗi — kế hoạch kiểm thử</v>
+        <v>Danh sách ưu tiên các tính năng, yêu cầu và công việc cần thực hiện cho sản phẩm — danh sách công việc tích lũy</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Sprint là một khung thời gian lặp đi lặp lại có độ dài cố định (thường từ 1-4 tuần) để tạo ra một phần tăng trưởng sản phẩm có thể bàn giao.</v>
       </c>
       <c r="F4" t="str">
+        <v>Quy trình kiểm thử hiệu năng tải trang web trước khi bàn giao cho khách hàng — kiểm thử tải</v>
+      </c>
+      <c r="G4" t="str">
         <v>Một khoảng thời gian cố định (thường từ 1-4 tuần) để team hoàn thành một lượng công việc cam kết — khung thời gian lặp</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
+        <v>Việc viết tài liệu thiết kế chi tiết kéo dài trong 3 tháng đầu dự án — giai đoạn thiết kế đặc tả</v>
+      </c>
+      <c r="I4" t="str">
         <v>Một cuộc họp khẩn cấp khi dự án gặp sự cố nghiêm trọng trên môi trường production — họp xử lý khủng hoảng</v>
       </c>
-      <c r="H4" t="str">
-        <v>Quy trình kiểm thử hiệu năng tải trang web trước khi bàn giao cho khách hàng — kiểm thử tải</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Việc viết tài liệu thiết kế chi tiết kéo dài trong 3 tháng đầu dự án — giai đoạn thiết kế đặc tả</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>User Story là công cụ mô tả tính năng ngắn gọn, được viết từ góc nhìn và ngôn ngữ của người dùng cuối để mô tả giá trị họ mong muốn.</v>
       </c>
       <c r="F5" t="str">
+        <v>Kiểm thử viên chịu trách nhiệm tìm lỗi trong hệ thống — góc nhìn kiểm thử viên</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Giám đốc dự án quản lý chi phí và tiến độ chung — góc nhìn quản lý</v>
+      </c>
+      <c r="H5" t="str">
         <v>Người dùng cuối hoặc khách hàng sử dụng sản phẩm — góc nhìn người dùng</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Lập trình viên chịu trách nhiệm viết mã nguồn cho tính năng — góc nhìn nhà phát triển</v>
       </c>
-      <c r="H5" t="str">
-        <v>Kiểm thử viên chịu trách nhiệm tìm lỗi trong hệ thống — góc nhìn kiểm thử viên</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Giám đốc dự án quản lý chi phí và tiến độ chung — góc nhìn quản lý</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -591,13 +591,13 @@
         <v>Định nghĩa các tiêu chuẩn chất lượng bắt buộc để một phần việc được coi là hoàn thành — tiêu chuẩn chất lượng</v>
       </c>
       <c r="G6" t="str">
+        <v>Định nghĩa tiến độ thời gian cần thiết để hoàn thành toàn bộ dự án — tiến độ dự án</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Bảng phân chia công việc cho từng thành viên trong cuộc họp Daily Scrum — bảng phân chia tác vụ</v>
+      </c>
+      <c r="I6" t="str">
         <v>Danh sách các công việc chưa được làm trong Sprint hiện tại — danh sách backlog</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Định nghĩa tiến độ thời gian cần thiết để hoàn thành toàn bộ dự án — tiến độ dự án</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Bảng phân chia công việc cho từng thành viên trong cuộc họp Daily Scrum — bảng phân chia tác vụ</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -623,13 +623,13 @@
         <v>Các thành viên chia sẻ những gì đã làm, sẽ làm và các khó khăn gặp phải — đồng bộ hóa tiến độ</v>
       </c>
       <c r="G7" t="str">
+        <v>BA và PO ngồi viết lại toàn bộ tài liệu đặc tả yêu cầu người dùng — viết đặc tả</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Quản lý dự án phê bình các thành viên làm việc chậm tiến độ — đánh giá nhân sự</v>
+      </c>
+      <c r="I7" t="str">
         <v>Lập trình viên demo trực tiếp các tính năng đã code cho khách hàng duyệt — duyệt tính năng</v>
-      </c>
-      <c r="H7" t="str">
-        <v>BA và PO ngồi viết lại toàn bộ tài liệu đặc tả yêu cầu người dùng — viết đặc tả</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Quản lý dự án phê bình các thành viên làm việc chậm tiến độ — đánh giá nhân sự</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Product Owner (PO) chịu trách nhiệm quản lý Product Backlog, bao gồm việc viết, sắp xếp và tối ưu hóa thứ tự ưu tiên của các backlog item.</v>
       </c>
       <c r="F9" t="str">
+        <v>Project Manager (PM) — người chịu trách nhiệm về tiến độ và chi phí</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Lead Developer — người chịu trách nhiệm về kiến trúc kỹ thuật</v>
+      </c>
+      <c r="H9" t="str">
         <v>Product Owner (PO) — người chịu trách nhiệm về giá trị sản phẩm</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>Scrum Master — người điều phối quy trình Scrum</v>
       </c>
-      <c r="H9" t="str">
-        <v>Lead Developer — người chịu trách nhiệm về kiến trúc kỹ thuật</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Project Manager (PM) — người chịu trách nhiệm về tiến độ và chi phí</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -719,10 +719,10 @@
         <v>Sprint Retrospective — họp cải tiến quy trình làm việc của team</v>
       </c>
       <c r="G10" t="str">
+        <v>Sprint Planning — họp lên kế hoạch cho Sprint tiếp theo</v>
+      </c>
+      <c r="H10" t="str">
         <v>Sprint Review — họp demo sản phẩm cho khách hàng xem</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Sprint Planning — họp lên kế hoạch cho Sprint tiếp theo</v>
       </c>
       <c r="I10" t="str">
         <v>Daily Scrum — họp đồng bộ công việc hàng ngày</v>
@@ -748,19 +748,19 @@
         <v>Định dạng Given (bối cảnh) - When (hành động) - Then (kết quả) giúp làm rõ kịch bản hành vi của hệ thống dưới các điều kiện biên nghiệp vụ.</v>
       </c>
       <c r="F11" t="str">
+        <v>Yêu cầu Dev viết code bằng ngôn ngữ lập trình Python thay vì Javascript — chỉ định ngôn ngữ</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Tính toán chính xác số dòng code mà lập trình viên cần viết — đo lường dòng code</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Để khách hàng tự động cài đặt ứng dụng vào máy tính cá nhân — cài đặt phần mềm</v>
+      </c>
+      <c r="I11" t="str">
         <v>Mô tả hành vi hệ thống rõ ràng dưới các điều kiện cụ thể để Dev và QA dễ hiểu — đặc tả kịch bản hành vi</v>
       </c>
-      <c r="G11" t="str">
-        <v>Yêu cầu Dev viết code bằng ngôn ngữ lập trình Python thay vì Javascript — chỉ định ngôn ngữ</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Tính toán chính xác số dòng code mà lập trình viên cần viết — đo lường dòng code</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Để khách hàng tự động cài đặt ứng dụng vào máy tính cá nhân — cài đặt phần mềm</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
